--- a/Result/profitability/6179.xlsx
+++ b/Result/profitability/6179.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.163336342344337e-17</v>
+        <v>0.225</v>
       </c>
       <c r="N2" t="n">
-        <v>9.440000000000001</v>
+        <v>11.85875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06249999999999995</v>
+        <v>0.008749999999999945</v>
       </c>
       <c r="N3" t="n">
-        <v>13.445</v>
+        <v>14.0225</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1675000000000001</v>
+        <v>-0.07000000000000006</v>
       </c>
       <c r="N4" t="n">
-        <v>15.21375</v>
+        <v>15.71875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2362500000000001</v>
+        <v>-0.1912500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>17.3225</v>
+        <v>18.40125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>-0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.33125</v>
+        <v>-0.1962500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>20.94875</v>
+        <v>21.59</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3712500000000001</v>
+        <v>-0.2262500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>24.31625</v>
+        <v>24.8425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.39375</v>
+        <v>-0.3200000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>25.99875</v>
+        <v>26.77625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.04</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4225000000000001</v>
+        <v>-0.4225</v>
       </c>
       <c r="N9" t="n">
         <v>27.245</v>
@@ -1772,7 +1772,7 @@
         <v>-0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3225000000000001</v>
+        <v>-0.3225</v>
       </c>
       <c r="N11" t="n">
         <v>29.3375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6179</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2369</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E75" t="n">
+        <v>355</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>271</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-91</v>
+      </c>
+      <c r="J75" t="n">
+        <v>180</v>
+      </c>
+      <c r="K75" t="n">
+        <v>152</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1924999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.445000000000002</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.185185185185185</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.220000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.7108571428571429</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.361198738170347</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
